--- a/term/CodeSystem-CareSocialCodes.xlsx
+++ b/term/CodeSystem-CareSocialCodes.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="299">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0</t>
+    <t>2.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-31T13:18:46+01:00</t>
+    <t>2025-08-21T08:46:07+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -177,15 +177,6 @@
     <t>VUM Borgerens ressourcer i forhold til indsatsen</t>
   </si>
   <si>
-    <t>54c4ffea-7caf-4edc-8aa9-ef6e0be26c4c</t>
-  </si>
-  <si>
-    <t>FSIII helhedsvurdering</t>
-  </si>
-  <si>
-    <t>Sagsvurdering, der sammenholder resultaterne af en myndighedsudredning og den øvrige sagsoplysning med henblik på at træffe en afgørelse</t>
-  </si>
-  <si>
     <t>7b41185e-eeb4-437d-8120-5d51bbd27a79</t>
   </si>
   <si>
@@ -543,15 +534,6 @@
     <t>udførelse af terapeutfaglig udredning jævnfør FSIII</t>
   </si>
   <si>
-    <t>e70c66c0-a939-493b-8ea8-5b7e7b48ba1a</t>
-  </si>
-  <si>
-    <t>generelle oplysninger, FSIII</t>
-  </si>
-  <si>
-    <t>indhentning af generelle oplysninger jævnfør FSIII</t>
-  </si>
-  <si>
     <t>10deb210-e7e1-4d56-9531-b9ff2102126e</t>
   </si>
   <si>
@@ -562,6 +544,15 @@
   </si>
   <si>
     <t>Det planlagte indsatsforløb er en social indsats, som defineret af FFB, med tilhørende ydelser, målgruppe og tilbud</t>
+  </si>
+  <si>
+    <t>01302bcb-c7f3-42c4-8ded-68e33da064eb</t>
+  </si>
+  <si>
+    <t>Lettilgængelige tilbud til børn og unge i psykisk mistrivsel</t>
+  </si>
+  <si>
+    <t>Forløbskode for lettilgængelige tilbud til børn og unge i psykisk mistrivsel.</t>
   </si>
   <si>
     <t>4fd6c23a-6ff3-4251-ac37-3ca095027b5b</t>
@@ -896,6 +887,30 @@
   </si>
   <si>
     <t>Borger har behov, men har foretaget et aktivt fravalg pga. den omkostning der er forbundet med transport til det sted indsatsen tilbydes</t>
+  </si>
+  <si>
+    <t>880028ec-5f16-4242-ba53-57a902094d5b</t>
+  </si>
+  <si>
+    <t>Deltagere i kontakt</t>
+  </si>
+  <si>
+    <t>ca228a58-bd0e-4b0e-81ce-3866adc26535</t>
+  </si>
+  <si>
+    <t>Barn/ung deltager</t>
+  </si>
+  <si>
+    <t>Behandler og barn/ung i målgruppen (5-17år) og evt. forældre, værger el.lign. er til stede. Barnet/den unge er genstand for journaloptagelsen.</t>
+  </si>
+  <si>
+    <t>d3578249-10df-4051-851d-3986b1570bee</t>
+  </si>
+  <si>
+    <t>Omsorgsperson uden barn/ung</t>
+  </si>
+  <si>
+    <t>Behandling hvor kun behandler og forældre, værger el.lign. til barn/ung er til stede. Barnet/den unge er genstand for journalen.</t>
   </si>
 </sst>
 </file>
@@ -1205,7 +1220,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D90"/>
+  <dimension ref="A1:D92"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1294,7 +1309,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B7" t="s" s="2">
         <v>54</v>
@@ -1303,18 +1318,18 @@
         <v>55</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B8" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="C8" t="s" s="2">
         <v>57</v>
-      </c>
-      <c r="C8" t="s" s="2">
-        <v>58</v>
       </c>
       <c r="D8" t="s" s="2">
         <v>58</v>
@@ -1392,7 +1407,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B14" t="s" s="2">
         <v>74</v>
@@ -1406,7 +1421,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B15" t="s" s="2">
         <v>77</v>
@@ -1518,21 +1533,21 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>43</v>
+        <v>101</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D23" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>104</v>
+        <v>40</v>
       </c>
       <c r="B24" t="s" s="2">
         <v>105</v>
@@ -1546,7 +1561,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B25" t="s" s="2">
         <v>108</v>
@@ -1644,7 +1659,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>129</v>
@@ -1653,18 +1668,18 @@
         <v>130</v>
       </c>
       <c r="D32" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B33" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="C33" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="C33" t="s" s="2">
-        <v>133</v>
       </c>
       <c r="D33" t="s" s="2">
         <v>133</v>
@@ -1686,7 +1701,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>137</v>
@@ -1695,18 +1710,18 @@
         <v>138</v>
       </c>
       <c r="D35" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B36" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="C36" t="s" s="2">
         <v>140</v>
-      </c>
-      <c r="C36" t="s" s="2">
-        <v>141</v>
       </c>
       <c r="D36" t="s" s="2">
         <v>141</v>
@@ -1779,32 +1794,32 @@
         <v>155</v>
       </c>
       <c r="D41" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B42" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="C42" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="C42" t="s" s="2">
-        <v>158</v>
-      </c>
       <c r="D42" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B43" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="C43" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="C43" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="D43" t="s" s="2">
         <v>160</v>
@@ -1868,7 +1883,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B48" t="s" s="2">
         <v>173</v>
@@ -1877,7 +1892,7 @@
         <v>174</v>
       </c>
       <c r="D48" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="49">
@@ -1885,27 +1900,27 @@
         <v>43</v>
       </c>
       <c r="B49" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="C49" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="D49" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="C49" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="D49" t="s" s="2">
-        <v>178</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B50" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="C50" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="D50" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="C50" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="D50" t="s" s="2">
-        <v>180</v>
       </c>
     </row>
     <row r="51">
@@ -1913,24 +1928,24 @@
         <v>43</v>
       </c>
       <c r="B51" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="C51" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="D51" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="C51" t="s" s="2">
-        <v>60</v>
-      </c>
-      <c r="D51" t="s" s="2">
-        <v>182</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>43</v>
+        <v>101</v>
       </c>
       <c r="B52" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="C52" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="C52" t="s" s="2">
-        <v>69</v>
       </c>
       <c r="D52" t="s" s="2">
         <v>184</v>
@@ -1938,7 +1953,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B53" t="s" s="2">
         <v>185</v>
@@ -1952,27 +1967,27 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>104</v>
+        <v>43</v>
       </c>
       <c r="B54" t="s" s="2">
         <v>188</v>
       </c>
       <c r="C54" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="D54" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="D54" t="s" s="2">
-        <v>190</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>43</v>
+        <v>101</v>
       </c>
       <c r="B55" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="C55" t="s" s="2">
         <v>191</v>
-      </c>
-      <c r="C55" t="s" s="2">
-        <v>72</v>
       </c>
       <c r="D55" t="s" s="2">
         <v>192</v>
@@ -1980,7 +1995,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B56" t="s" s="2">
         <v>193</v>
@@ -1994,7 +2009,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>104</v>
+        <v>40</v>
       </c>
       <c r="B57" t="s" s="2">
         <v>196</v>
@@ -2008,7 +2023,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B58" t="s" s="2">
         <v>199</v>
@@ -2036,7 +2051,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B60" t="s" s="2">
         <v>205</v>
@@ -2045,18 +2060,18 @@
         <v>206</v>
       </c>
       <c r="D60" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B61" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="C61" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="C61" t="s" s="2">
-        <v>209</v>
       </c>
       <c r="D61" t="s" s="2">
         <v>209</v>
@@ -2078,7 +2093,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B63" t="s" s="2">
         <v>213</v>
@@ -2087,18 +2102,18 @@
         <v>214</v>
       </c>
       <c r="D63" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B64" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="C64" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="C64" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="D64" t="s" s="2">
         <v>217</v>
@@ -2162,7 +2177,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B69" t="s" s="2">
         <v>230</v>
@@ -2176,7 +2191,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B70" t="s" s="2">
         <v>233</v>
@@ -2232,7 +2247,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B74" t="s" s="2">
         <v>245</v>
@@ -2241,18 +2256,18 @@
         <v>246</v>
       </c>
       <c r="D74" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B75" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="C75" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="C75" t="s" s="2">
-        <v>249</v>
       </c>
       <c r="D75" t="s" s="2">
         <v>249</v>
@@ -2316,7 +2331,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B80" t="s" s="2">
         <v>262</v>
@@ -2330,7 +2345,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B81" t="s" s="2">
         <v>265</v>
@@ -2381,7 +2396,7 @@
         <v>275</v>
       </c>
       <c r="D84" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="85">
@@ -2389,10 +2404,10 @@
         <v>43</v>
       </c>
       <c r="B85" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="C85" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="C85" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="D85" t="s" s="2">
         <v>278</v>
@@ -2400,7 +2415,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>43</v>
+        <v>101</v>
       </c>
       <c r="B86" t="s" s="2">
         <v>279</v>
@@ -2414,7 +2429,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B87" t="s" s="2">
         <v>282</v>
@@ -2428,7 +2443,7 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B88" t="s" s="2">
         <v>285</v>
@@ -2442,7 +2457,7 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B89" t="s" s="2">
         <v>288</v>
@@ -2456,7 +2471,7 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>104</v>
+        <v>40</v>
       </c>
       <c r="B90" t="s" s="2">
         <v>291</v>
@@ -2465,7 +2480,35 @@
         <v>292</v>
       </c>
       <c r="D90" t="s" s="2">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B91" t="s" s="2">
         <v>293</v>
+      </c>
+      <c r="C91" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="D91" t="s" s="2">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="C92" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="D92" t="s" s="2">
+        <v>298</v>
       </c>
     </row>
   </sheetData>

--- a/term/CodeSystem-CareSocialCodes.xlsx
+++ b/term/CodeSystem-CareSocialCodes.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="302">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.3.0</t>
+    <t>2.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-21T08:46:07+02:00</t>
+    <t>2026-04-21T22:08:40+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -138,196 +138,112 @@
     <t>1</t>
   </si>
   <si>
-    <t>95ec4535-8fe8-4296-867c-35de421794cf</t>
-  </si>
-  <si>
-    <t>evaluering</t>
+    <t>10deb210-e7e1-4d56-9531-b9ff2102126e</t>
+  </si>
+  <si>
+    <t>Planlagt indsatsforløb</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>effe55c7-572c-4a99-8fb4-2a9dda2f6572</t>
-  </si>
-  <si>
-    <t>FFB støttebehovsvurdering</t>
-  </si>
-  <si>
-    <t>Angiver, hvor stort et behov borgeren har for hjælp og støtte.</t>
-  </si>
-  <si>
-    <t>053a301d-1bb8-4cc4-b781-87825ecf0ef8</t>
-  </si>
-  <si>
-    <t>FFB vurdering af borgers situation</t>
-  </si>
-  <si>
-    <t>Vurdering der sammenholder oplysninger fra udredning mhp en samlet faglig analyse og konklusion.</t>
-  </si>
-  <si>
-    <t>3f7a8ca0-afca-4b0d-8773-a99b5f2f8aaf</t>
-  </si>
-  <si>
-    <t>VUM Borgerens perspektiv på indsatsen</t>
-  </si>
-  <si>
-    <t>f52887de-023f-4193-b6b0-4b0a37b1cffc</t>
-  </si>
-  <si>
-    <t>VUM Borgerens ressourcer i forhold til indsatsen</t>
-  </si>
-  <si>
-    <t>7b41185e-eeb4-437d-8120-5d51bbd27a79</t>
-  </si>
-  <si>
-    <t>Indsats/ydelses-anmodning</t>
-  </si>
-  <si>
-    <t>4a297733-4d66-4726-a933-590d55cf91e0</t>
+    <t>01302bcb-c7f3-42c4-8ded-68e33da064eb</t>
+  </si>
+  <si>
+    <t>Lettilgængelige tilbud til børn og unge i psykisk mistrivsel</t>
+  </si>
+  <si>
+    <t>Forløbskode for lettilgængelige tilbud til børn og unge i psykisk mistrivsel.</t>
+  </si>
+  <si>
+    <t>e459386d-1474-4c31-89c5-c8bc7a25e3d4</t>
   </si>
   <si>
     <t>Social indsats</t>
   </si>
   <si>
-    <t>Der anmodes om en social indsats</t>
-  </si>
-  <si>
-    <t>ad865929-7363-4b2d-a271-01993181fbaf</t>
-  </si>
-  <si>
-    <t>Kommunal pleje og omsorg</t>
-  </si>
-  <si>
-    <t>Der anmodes om kommunal pleje og omsorg fx hjemmepleje til ældre borger.</t>
-  </si>
-  <si>
-    <t>490ab7be-ddb1-4a54-baf1-009fe6e8a83b</t>
-  </si>
-  <si>
-    <t>Kommunal sygepleje</t>
-  </si>
-  <si>
-    <t>Der anmodes om kommunal sygepleje.</t>
-  </si>
-  <si>
-    <t>a71921ea-fe83-441d-933b-cc21d0b3c8c3</t>
+    <t>Det planlagte indsatsforløb er en social indsats, som defineret af FFB, med tilhørende ydelser, målgruppe og tilbud</t>
+  </si>
+  <si>
+    <t>4fd6c23a-6ff3-4251-ac37-3ca095027b5b</t>
   </si>
   <si>
     <t>Kommunal Sundhedsfremme og forebyggelse</t>
   </si>
   <si>
-    <t>Der anmodes om kommunal sundhedsfremme og forebyggelse efter SUL §119.</t>
-  </si>
-  <si>
-    <t>7fc66c15-0cb3-4c89-9e18-f3a01e6a6592</t>
+    <t>Det planlagte indsatsforløb vedrører sundhedsfremme og forebyggelse efter §119.</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>5c160c02-e858-4c1f-925a-71ed64844749</t>
+  </si>
+  <si>
+    <t>Interventionsforløb efter §119</t>
+  </si>
+  <si>
+    <t>Et planlagt §119 indsatsforløb, som udelukkende indeholder interventioner, og som leveres samlet. Med interventioner menes indsatser, der søger at forbedre borgers tilstand. For §119 kunne et interventionsforløb fx være et KOL-træningshold der indeholder indsatserne fysisk træning og funktionstræning.</t>
+  </si>
+  <si>
+    <t>9791e55a-656f-47eb-8fd5-c4a06b0a4662</t>
+  </si>
+  <si>
+    <t>Opfølgningsforløb efter §119</t>
+  </si>
+  <si>
+    <t>Planlagt indsatsforløb der består af opfølgningsindsatser. Anvendes hvis der i forvejen planlægges opfølgning ved flere forskellige lejligheder fx efter 2,4 og 6 måneder.</t>
+  </si>
+  <si>
+    <t>ddd2f670-5ec7-4f9c-9a2c-aee25cb133bf</t>
   </si>
   <si>
     <t>Kommunal genoptræning efter sygehusophold</t>
   </si>
   <si>
-    <t>Der anmodes om kommunal genoptræning efter sygehusophold efter SUL §140.</t>
-  </si>
-  <si>
-    <t>d267ac44-8d7f-43e9-8535-ab3da350649f</t>
-  </si>
-  <si>
-    <t>Kommunalt hjælpemiddelområde</t>
-  </si>
-  <si>
-    <t>Der anmodes om hjælpemidler og lignende, der ligger indenfor det kommunale hjælpemiddelområde dvs § 112, § 113, § 114, § 116 i Serviceloven.</t>
-  </si>
-  <si>
-    <t>b5731132-f6b9-4a47-995d-681d2b755d4f</t>
-  </si>
-  <si>
-    <t>Kilde</t>
-  </si>
-  <si>
-    <t>Person der er kilde til oplysning eller vurdering</t>
-  </si>
-  <si>
-    <t>25b4e705-2e9a-47a2-b11a-c829316b9d3a</t>
-  </si>
-  <si>
-    <t>Borger</t>
-  </si>
-  <si>
-    <t>Borger er kilde til oplysning eller vurdering</t>
-  </si>
-  <si>
-    <t>f6ea2920-7dde-491e-a489-6b99a3904069</t>
-  </si>
-  <si>
-    <t>Sagsbehandler</t>
-  </si>
-  <si>
-    <t>Sagsbehandler er kilde til oplysning eller vurdering</t>
-  </si>
-  <si>
-    <t>166d2437-4e47-4a52-bd94-cdbe91086ca6</t>
-  </si>
-  <si>
-    <t>Pårørende alene</t>
-  </si>
-  <si>
-    <t>Pårørende er alene, uden input fra borger, kilde til oplysninger eller vuderderinger. Fx WHO 5 spørgeskema for svækket ældre borger udfyldt af datter.</t>
-  </si>
-  <si>
-    <t>329774f9-7700-47cf-9c00-63765d9e8078</t>
-  </si>
-  <si>
-    <t>Medarbejder og pårørende alene</t>
-  </si>
-  <si>
-    <t>En medarbejder og pårørende er sammen, men uden input fra borger, kilde til oplysning eller vurdering. Fx PUF spørgeskema i sundhedsplejen.</t>
-  </si>
-  <si>
-    <t>12428e48-7df8-441f-9a89-d92bb7874066</t>
-  </si>
-  <si>
-    <t>Borger støttet af medarbejder</t>
-  </si>
-  <si>
-    <t>Borger fik hjælp af en medarbejder til at komme med oplysninger eller vurderinger. Fx ældre borger der får hjælp til at udfylde WHO5 spørgeskema.</t>
-  </si>
-  <si>
-    <t>8fe80acb-2c2a-4f10-b2b8-ddb77d2f69dc</t>
-  </si>
-  <si>
-    <t>Medarbejder alene</t>
-  </si>
-  <si>
-    <t>Medarbejderen er alene kilde til oplysning eller vurdering. Fx AIMS skema i sundhedsplejen.</t>
-  </si>
-  <si>
-    <t>b66dc78a-a673-43fc-8ac0-1e859ba626e0</t>
-  </si>
-  <si>
-    <t>Borger støttet af pårørende</t>
-  </si>
-  <si>
-    <t>Borger fik hjælp af en pårørende til at komme med oplysninger eller vurderinger. Fx ældre borger der får hjælp til at udfylde WHO5 spørgeskema.</t>
-  </si>
-  <si>
-    <t>63338442-7b2e-405b-acc0-142361ef19f1</t>
-  </si>
-  <si>
-    <t>Andre</t>
-  </si>
-  <si>
-    <t>Andre end borger og sagsbehandler er kilde til oplysning eller vurdering. Fx læge, pårørende og udfører. Denne definition af andre, bruges kun på voksensocialområdet.</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>f00a6844-1005-401d-965d-1c5859df7beb</t>
-  </si>
-  <si>
-    <t>Udfører</t>
-  </si>
-  <si>
-    <t>Udfører er kilde til oplysning eller vurdering</t>
+    <t>Det planlagte indsatsforløb er genoptræning efter sundhedslovens §140.</t>
+  </si>
+  <si>
+    <t>4863001e-14c7-4be8-a2da-e4f21a4b6ac4</t>
+  </si>
+  <si>
+    <t>Opfølgningsforløb efter §140</t>
+  </si>
+  <si>
+    <t>Planlagt indsatsforløb efter §140 der består af opfølgningsindsatser. Anvendes hvis der i forvejen planlægges opfølgning ved flere forskellige lejligheder fx efter 2,4 og 6 måneder.</t>
+  </si>
+  <si>
+    <t>f15b2663-94d9-4d0c-a5de-d8bd8e1e4ebb</t>
+  </si>
+  <si>
+    <t>Interventionsforløb efter §140</t>
+  </si>
+  <si>
+    <t>Et planlagt §140 indsatsforløb, som udelukkende indeholder interventioner, og som leveres samlet. Med interventioner menes indsatser, der søger at forbedre borgers tilstand. For §140 kunne et interventionsforløb fx være et Knæ-genoptræningshold der indeholder indsatserne fysisk træning, funktionstræning og vejledning og undervisning.</t>
+  </si>
+  <si>
+    <t>11266a8f-5795-42ab-88ec-4fe5c6c28e80</t>
+  </si>
+  <si>
+    <t>Målfokus</t>
+  </si>
+  <si>
+    <t>66959f77-6e2a-4574-8423-3ff097f8b9fa</t>
+  </si>
+  <si>
+    <t>funktionsevneniveau</t>
+  </si>
+  <si>
+    <t>målet udtrykkes i form af et funktionsevneniveau, som kan være et FFB funktionsevneniveau eller FSIII tilstandsniveau</t>
+  </si>
+  <si>
+    <t>90c48f03-f194-4b2f-ad7d-6cba1069ae48</t>
+  </si>
+  <si>
+    <t>måltype</t>
+  </si>
+  <si>
+    <t>målet udtrykkes i form af en måltype, måltypen er den forventede ændring i tilstanden givet indsatsen</t>
   </si>
   <si>
     <t>25303acd-dcaf-4a8e-a8a3-3961a43858aa</t>
@@ -339,6 +255,33 @@
     <t>aktivitet der foretages ved kommunal kontakt.</t>
   </si>
   <si>
+    <t>829ac647-c7fc-4964-836b-f708d886e0e3</t>
+  </si>
+  <si>
+    <t>oplysning</t>
+  </si>
+  <si>
+    <t>oplysning er foretaget ved kontakt</t>
+  </si>
+  <si>
+    <t>9269c9a2-8220-447b-a127-811275b41062</t>
+  </si>
+  <si>
+    <t>vurdering/bevilling</t>
+  </si>
+  <si>
+    <t>vurdering og/eller bevilling er foretaget ved kontakt</t>
+  </si>
+  <si>
+    <t>9f03dfbb-7a97-45a5-94db-d4c3501714a9</t>
+  </si>
+  <si>
+    <t>opfølgning</t>
+  </si>
+  <si>
+    <t>opfølgning foretaget ved kontakt</t>
+  </si>
+  <si>
     <t>bb6fc544-7f4f-4b50-8868-1431e0df2381</t>
   </si>
   <si>
@@ -348,22 +291,13 @@
     <t>observation foretaget ved kontakt</t>
   </si>
   <si>
-    <t>9f03dfbb-7a97-45a5-94db-d4c3501714a9</t>
-  </si>
-  <si>
-    <t>opfølgning</t>
-  </si>
-  <si>
-    <t>opfølgning foretaget ved kontakt</t>
-  </si>
-  <si>
-    <t>829ac647-c7fc-4964-836b-f708d886e0e3</t>
-  </si>
-  <si>
-    <t>oplysning</t>
-  </si>
-  <si>
-    <t>oplysning er foretaget ved kontakt</t>
+    <t>4530b499-d74b-4d2e-9df9-247047fb231d</t>
+  </si>
+  <si>
+    <t>udførelse af indsats</t>
+  </si>
+  <si>
+    <t>Indsats udført ved kontakt</t>
   </si>
   <si>
     <t>15775b0a-7ec6-469e-9d3c-a81fbc9a1b45</t>
@@ -375,6 +309,15 @@
     <t>Akutindsats, bevilget af læge eller akutteam, udført ved kontakt</t>
   </si>
   <si>
+    <t>784275f1-6822-4a88-b361-d958007d5253</t>
+  </si>
+  <si>
+    <t>udførelse af planlagt indsats</t>
+  </si>
+  <si>
+    <t>Planlagt indsats udført ved kontakt</t>
+  </si>
+  <si>
     <t>c03b426a-4348-407f-b343-f4baa9759c72</t>
   </si>
   <si>
@@ -384,22 +327,148 @@
     <t>Indsats, der ikke i forvejen var bevilget, udført ved kontakt</t>
   </si>
   <si>
-    <t>784275f1-6822-4a88-b361-d958007d5253</t>
-  </si>
-  <si>
-    <t>udførelse af planlagt indsats</t>
-  </si>
-  <si>
-    <t>Planlagt indsats udført ved kontakt</t>
-  </si>
-  <si>
-    <t>9269c9a2-8220-447b-a127-811275b41062</t>
-  </si>
-  <si>
-    <t>vurdering/bevilling</t>
-  </si>
-  <si>
-    <t>vurdering og/eller bevilling er foretaget ved kontakt</t>
+    <t>253bbdc0-c4ca-4e77-9d3e-3a9e51281636</t>
+  </si>
+  <si>
+    <t>Mål/formål</t>
+  </si>
+  <si>
+    <t>0bb3daef-538d-45dc-b444-abdbcb63f6bc</t>
+  </si>
+  <si>
+    <t>FFB indsatsmål</t>
+  </si>
+  <si>
+    <t>Indsatsmål i FFB - er de konkrete faglige mål der arbejdes med, og som er knyttet til tilstande og opfølgninger</t>
+  </si>
+  <si>
+    <t>416fe27d-3ccf-4390-8742-8b52a9d8dc78</t>
+  </si>
+  <si>
+    <t>FFB borgers mål og ønsker</t>
+  </si>
+  <si>
+    <t>Borgers mål og ønsker som specificeret af FFB. Det er overordnet og er som udtrykt af borger</t>
+  </si>
+  <si>
+    <t>424827b1-23aa-4848-962b-56ee47def560</t>
+  </si>
+  <si>
+    <t>Indsatsformål</t>
+  </si>
+  <si>
+    <t>Det overordnede formål med hele indsatsen (Defineret af FFB men bruges også for FSIII)</t>
+  </si>
+  <si>
+    <t>6746d4af-145a-4bfd-a672-05c0cf11b53b</t>
+  </si>
+  <si>
+    <t>FFB delmål</t>
+  </si>
+  <si>
+    <t>Delmål i FFB, ligger under indsatsmål, og er som udtrykt af udfører</t>
+  </si>
+  <si>
+    <t>ca552020-6ed1-4cdc-b0d4-32697f1f27ad</t>
+  </si>
+  <si>
+    <t>FSIII tilstandsmål</t>
+  </si>
+  <si>
+    <t>Tilstandsmål som defineret af FSIII - ofte i form af en forventet tilstand</t>
+  </si>
+  <si>
+    <t>ffb9886b-d04e-46b1-9165-a400f91f822b</t>
+  </si>
+  <si>
+    <t>Borgers ønsker og mål</t>
+  </si>
+  <si>
+    <t>2c059407-fed5-4852-92d8-6bb5ad63d7bb</t>
+  </si>
+  <si>
+    <t>Begrundelse for indsatsophør</t>
+  </si>
+  <si>
+    <t>Begrundelse for, at kommunale indsatser ophører</t>
+  </si>
+  <si>
+    <t>4bbf6d6a-a1c6-41c2-b8c1-7352b7378adf</t>
+  </si>
+  <si>
+    <t>Ikke yderligere behov (borger-vurderet)</t>
+  </si>
+  <si>
+    <t>Borger vurderer, at han/hun ikke har yderligere behov og afslutter derfor før tid</t>
+  </si>
+  <si>
+    <t>82e99421-31da-4915-96ed-168ccfa1d20c</t>
+  </si>
+  <si>
+    <t>Hændelse medfører ophør</t>
+  </si>
+  <si>
+    <t>Hændelse, som ikke er et aktivt fravalg eller en behovsvurdering medfører ophør. Det kan fx være en længere hospitalsindlæggelse, eller at borger flytter.</t>
+  </si>
+  <si>
+    <t>a63b6aa6-7d56-4e67-a5b3-d73f6d262af5</t>
+  </si>
+  <si>
+    <t>Ikke yderligere behov (fagperson-vurderet)</t>
+  </si>
+  <si>
+    <t>Fagperson vurderer, at borger ikke har yderligere behov og afslutter derfor før tid</t>
+  </si>
+  <si>
+    <t>ef491570-7884-4acd-bcf7-43d6b2c64762</t>
+  </si>
+  <si>
+    <t>Borger har ikke henvendt sig eller er udeblevet</t>
+  </si>
+  <si>
+    <t>3a5a72b7-addf-4857-b80c-04e4246e3072</t>
+  </si>
+  <si>
+    <t>Aktivt fravalg</t>
+  </si>
+  <si>
+    <t>Borger har behov, men har foretaget et aktivt fravalg</t>
+  </si>
+  <si>
+    <t>0cd5734d-b663-47c6-a3da-6b14a937d144</t>
+  </si>
+  <si>
+    <t>Aktivt fravalg pga. anden sygdom</t>
+  </si>
+  <si>
+    <t>Borger har behov, men har foretaget et aktivt fravalg pga. anden sygdom</t>
+  </si>
+  <si>
+    <t>8371b769-4bfb-4ac8-b130-d91c54784a56</t>
+  </si>
+  <si>
+    <t>Aktivt fravalg pga. logistik ifm. transport</t>
+  </si>
+  <si>
+    <t>Borger har behov, men har foretaget et aktivt fravalg pga. den logistiske udfordring det er mht. transport, at nå frem til det sted indsatsen tilbydes</t>
+  </si>
+  <si>
+    <t>a3f2bd01-078b-486e-81be-797d192ad7bd</t>
+  </si>
+  <si>
+    <t>Aktivt fravalg pga. anden træning</t>
+  </si>
+  <si>
+    <t>Borger har behov, men har foretaget et aktivt fravalg fordi han/hun er påbegyndt træning i andet regi fx fitnesscenter</t>
+  </si>
+  <si>
+    <t>f8436c2e-af1c-44fe-939d-473b518dd01d</t>
+  </si>
+  <si>
+    <t>Aktivt fravalg pga. økonomi ifm. transport</t>
+  </si>
+  <si>
+    <t>Borger har behov, men har foretaget et aktivt fravalg pga. den omkostning der er forbundet med transport til det sted indsatsen tilbydes</t>
   </si>
   <si>
     <t>3762dd32-4123-43a8-815d-ec40d3697652</t>
@@ -426,285 +495,6 @@
     <t>Borger indforstået med henvendelse</t>
   </si>
   <si>
-    <t>253bbdc0-c4ca-4e77-9d3e-3a9e51281636</t>
-  </si>
-  <si>
-    <t>Mål/formål</t>
-  </si>
-  <si>
-    <t>416fe27d-3ccf-4390-8742-8b52a9d8dc78</t>
-  </si>
-  <si>
-    <t>FFB borgers mål og ønsker</t>
-  </si>
-  <si>
-    <t>Borgers mål og ønsker som specificeret af FFB. Det er overordnet og er som udtrykt af borger</t>
-  </si>
-  <si>
-    <t>6746d4af-145a-4bfd-a672-05c0cf11b53b</t>
-  </si>
-  <si>
-    <t>FFB delmål</t>
-  </si>
-  <si>
-    <t>Delmål i FFB, ligger under indsatsmål, og er som udtrykt af udfører</t>
-  </si>
-  <si>
-    <t>0bb3daef-538d-45dc-b444-abdbcb63f6bc</t>
-  </si>
-  <si>
-    <t>FFB indsatsmål</t>
-  </si>
-  <si>
-    <t>Indsatsmål i FFB - er de konkrete faglige mål der arbejdes med, og som er knyttet til tilstande og opfølgninger</t>
-  </si>
-  <si>
-    <t>ca552020-6ed1-4cdc-b0d4-32697f1f27ad</t>
-  </si>
-  <si>
-    <t>FSIII tilstandsmål</t>
-  </si>
-  <si>
-    <t>Tilstandsmål som defineret af FSIII - ofte i form af en forventet tilstand</t>
-  </si>
-  <si>
-    <t>424827b1-23aa-4848-962b-56ee47def560</t>
-  </si>
-  <si>
-    <t>Indsatsformål</t>
-  </si>
-  <si>
-    <t>Det overordnede formål med hele indsatsen (Defineret af FFB men bruges også for FSIII)</t>
-  </si>
-  <si>
-    <t>ffb9886b-d04e-46b1-9165-a400f91f822b</t>
-  </si>
-  <si>
-    <t>Borgers ønsker og mål</t>
-  </si>
-  <si>
-    <t>940f37e6-8a3d-483b-adac-be8af3268a5b</t>
-  </si>
-  <si>
-    <t>oplysningsaktivitet</t>
-  </si>
-  <si>
-    <t>95e787e0-5490-437d-ae4c-f3736644242f</t>
-  </si>
-  <si>
-    <t>afklarende samtale §119, FSIII</t>
-  </si>
-  <si>
-    <t>udførelse af afklarende samtale vedr. sundhedsfremme og forebyggelse jævnfør FSIII</t>
-  </si>
-  <si>
-    <t>e5a73b0e-a5d2-430e-931f-6156306ab00f</t>
-  </si>
-  <si>
-    <t>funktionsevnevurdering hjemmepleje, FSIII</t>
-  </si>
-  <si>
-    <t>udførelse af funktionsevnevurdering i hjemmeplejen jævnfør FSIII</t>
-  </si>
-  <si>
-    <t>f8ebd11a-04f3-4aa0-9786-406e8896c84d</t>
-  </si>
-  <si>
-    <t>socialfaglig udredning, VUM/FFB</t>
-  </si>
-  <si>
-    <t>udførelse af socialfaglig udredning som specificeret af VUM og FFB</t>
-  </si>
-  <si>
-    <t>47fd1468-89da-4803-9d7a-ecc039a30d92</t>
-  </si>
-  <si>
-    <t>sygeplejefaglig udredning, FSIII</t>
-  </si>
-  <si>
-    <t>udførelse af sygeplejefaglig udredning jævnfør FSIII</t>
-  </si>
-  <si>
-    <t>0f0f223c-abe3-4720-aab8-c257679a0a4e</t>
-  </si>
-  <si>
-    <t>terapeutfaglig udredning, FSIII</t>
-  </si>
-  <si>
-    <t>udførelse af terapeutfaglig udredning jævnfør FSIII</t>
-  </si>
-  <si>
-    <t>10deb210-e7e1-4d56-9531-b9ff2102126e</t>
-  </si>
-  <si>
-    <t>Planlagt indsatsforløb</t>
-  </si>
-  <si>
-    <t>e459386d-1474-4c31-89c5-c8bc7a25e3d4</t>
-  </si>
-  <si>
-    <t>Det planlagte indsatsforløb er en social indsats, som defineret af FFB, med tilhørende ydelser, målgruppe og tilbud</t>
-  </si>
-  <si>
-    <t>01302bcb-c7f3-42c4-8ded-68e33da064eb</t>
-  </si>
-  <si>
-    <t>Lettilgængelige tilbud til børn og unge i psykisk mistrivsel</t>
-  </si>
-  <si>
-    <t>Forløbskode for lettilgængelige tilbud til børn og unge i psykisk mistrivsel.</t>
-  </si>
-  <si>
-    <t>4fd6c23a-6ff3-4251-ac37-3ca095027b5b</t>
-  </si>
-  <si>
-    <t>Det planlagte indsatsforløb vedrører sundhedsfremme og forebyggelse efter §119.</t>
-  </si>
-  <si>
-    <t>9791e55a-656f-47eb-8fd5-c4a06b0a4662</t>
-  </si>
-  <si>
-    <t>Opfølgningsforløb efter §119</t>
-  </si>
-  <si>
-    <t>Planlagt indsatsforløb der består af opfølgningsindsatser. Anvendes hvis der i forvejen planlægges opfølgning ved flere forskellige lejligheder fx efter 2,4 og 6 måneder.</t>
-  </si>
-  <si>
-    <t>5c160c02-e858-4c1f-925a-71ed64844749</t>
-  </si>
-  <si>
-    <t>Interventionsforløb efter §119</t>
-  </si>
-  <si>
-    <t>Et planlagt §119 indsatsforløb, som udelukkende indeholder interventioner, og som leveres samlet. Med interventioner menes indsatser, der søger at forbedre borgers tilstand. For §119 kunne et interventionsforløb fx være et KOL-træningshold der indeholder indsatserne fysisk træning og funktionstræning.</t>
-  </si>
-  <si>
-    <t>ddd2f670-5ec7-4f9c-9a2c-aee25cb133bf</t>
-  </si>
-  <si>
-    <t>Det planlagte indsatsforløb er genoptræning efter sundhedslovens §140.</t>
-  </si>
-  <si>
-    <t>4863001e-14c7-4be8-a2da-e4f21a4b6ac4</t>
-  </si>
-  <si>
-    <t>Opfølgningsforløb efter §140</t>
-  </si>
-  <si>
-    <t>Planlagt indsatsforløb efter §140 der består af opfølgningsindsatser. Anvendes hvis der i forvejen planlægges opfølgning ved flere forskellige lejligheder fx efter 2,4 og 6 måneder.</t>
-  </si>
-  <si>
-    <t>f15b2663-94d9-4d0c-a5de-d8bd8e1e4ebb</t>
-  </si>
-  <si>
-    <t>Interventionsforløb efter §140</t>
-  </si>
-  <si>
-    <t>Et planlagt §140 indsatsforløb, som udelukkende indeholder interventioner, og som leveres samlet. Med interventioner menes indsatser, der søger at forbedre borgers tilstand. For §140 kunne et interventionsforløb fx være et Knæ-genoptræningshold der indeholder indsatserne fysisk træning, funktionstræning og vejledning og undervisning.</t>
-  </si>
-  <si>
-    <t>bf469e95-f9e3-45c7-bf15-ab7e8a85236f</t>
-  </si>
-  <si>
-    <t>Kontaktklasse</t>
-  </si>
-  <si>
-    <t>Type af kontakt. Beskriver leveringsmetode.</t>
-  </si>
-  <si>
-    <t>124be95d-6924-4609-9d2a-e7c73ae3ab3d</t>
-  </si>
-  <si>
-    <t>Skærmbesøg</t>
-  </si>
-  <si>
-    <t>Kontakten er foregået via skærm med mulighed for tændt kamera, så parterne har haft mulighed for at interagere ansigt til ansigt, og fremvise ting.</t>
-  </si>
-  <si>
-    <t>1b55a4b0-1156-4f58-b2df-b5c6014d9048</t>
-  </si>
-  <si>
-    <t>Telefonisk</t>
-  </si>
-  <si>
-    <t>Kontakten er foregået per telefon.</t>
-  </si>
-  <si>
-    <t>11266a8f-5795-42ab-88ec-4fe5c6c28e80</t>
-  </si>
-  <si>
-    <t>Målfokus</t>
-  </si>
-  <si>
-    <t>66959f77-6e2a-4574-8423-3ff097f8b9fa</t>
-  </si>
-  <si>
-    <t>funktionsevneniveau</t>
-  </si>
-  <si>
-    <t>målet udtrykkes i form af et funktionsevneniveau, som kan være et FFB funktionsevneniveau eller FSIII tilstandsniveau</t>
-  </si>
-  <si>
-    <t>90c48f03-f194-4b2f-ad7d-6cba1069ae48</t>
-  </si>
-  <si>
-    <t>måltype</t>
-  </si>
-  <si>
-    <t>målet udtrykkes i form af en måltype, måltypen er den forventede ændring i tilstanden givet indsatsen</t>
-  </si>
-  <si>
-    <t>6b29554d-0261-4ec4-bb16-022d81c7dfb7</t>
-  </si>
-  <si>
-    <t>Type genoptræningsplan</t>
-  </si>
-  <si>
-    <t>0c8e2bfc-1350-45d1-90da-c07e2645d073</t>
-  </si>
-  <si>
-    <t>Specialiseret</t>
-  </si>
-  <si>
-    <t>Midlertidig kopi af MedComs kode for genoptræning på specialieret niveau, som specificeret af den gode genoptræningsplan, https://svn.medcom.dk/svn/releases/Standarder/National%20Sygehus-Kommunesamarbejde/GGOP/Dokumentation/GGOP.pdf</t>
-  </si>
-  <si>
-    <t>8b962281-2ab6-4b10-9c91-4bac592d6d49</t>
-  </si>
-  <si>
-    <t>Basal</t>
-  </si>
-  <si>
-    <t>Almen genoptræning på basalt niveau</t>
-  </si>
-  <si>
-    <t>ffd81f78-352e-4589-a195-5350dd1df2a4</t>
-  </si>
-  <si>
-    <t>Almen</t>
-  </si>
-  <si>
-    <t>Midlertidig kopi af MedComs kode for genoptræning på alment niveau, som specificeret af den gode genoptræningsplan, https://svn.medcom.dk/svn/releases/Standarder/National%20Sygehus-Kommunesamarbejde/GGOP/Dokumentation/GGOP.pdf</t>
-  </si>
-  <si>
-    <t>b679c454-2da2-46dd-9425-0e52d4aa2bf3</t>
-  </si>
-  <si>
-    <t>Avanceret</t>
-  </si>
-  <si>
-    <t>Almen genoptræning på avanceret niveau</t>
-  </si>
-  <si>
-    <t>83c89857-8fb8-4163-97b1-eb1a56345c29</t>
-  </si>
-  <si>
-    <t>Rehabilitering</t>
-  </si>
-  <si>
-    <t>Midlertidig kopi af MedComs kode for rehabilitering på specialiseret niveau, som specificeret af den gode genoptræningsplan, https://svn.medcom.dk/svn/releases/Standarder/National%20Sygehus-Kommunesamarbejde/GGOP/Dokumentation/GGOP.pdf</t>
-  </si>
-  <si>
     <t>3f79cee2-b148-4f2c-9cbd-387820e74685</t>
   </si>
   <si>
@@ -714,6 +504,15 @@
     <t>Om der leveres individuelt eller gruppebaseret</t>
   </si>
   <si>
+    <t>284857a4-5e91-499a-a001-64d7f0b7038a</t>
+  </si>
+  <si>
+    <t>Digital levering af indsats</t>
+  </si>
+  <si>
+    <t>En applikation med fokus på adfærdsændring eller træning leverer indsatsen.</t>
+  </si>
+  <si>
     <t>2865f123-15a7-4a36-a514-32ea37c400ca</t>
   </si>
   <si>
@@ -721,15 +520,6 @@
   </si>
   <si>
     <t>Indsats leveres af en medarbejder, der interagerer med en gruppe som borgeren er del af.</t>
-  </si>
-  <si>
-    <t>8d12d74c-17da-47a7-a4fe-e69dbaec0a8c</t>
-  </si>
-  <si>
-    <t>Individuel indsats</t>
-  </si>
-  <si>
-    <t>Indsats leveres af en medarbejder i en-til-en interaktion.</t>
   </si>
   <si>
     <t>34cdd6ab-3da9-49e8-84dc-1cbf683d4fcf</t>
@@ -742,13 +532,316 @@
 Eksempler: Robotstøvsugning</t>
   </si>
   <si>
-    <t>284857a4-5e91-499a-a001-64d7f0b7038a</t>
-  </si>
-  <si>
-    <t>Digital levering af indsats</t>
-  </si>
-  <si>
-    <t>En applikation med fokus på adfærdsændring eller træning leverer indsatsen.</t>
+    <t>8d12d74c-17da-47a7-a4fe-e69dbaec0a8c</t>
+  </si>
+  <si>
+    <t>Individuel indsats</t>
+  </si>
+  <si>
+    <t>Indsats leveres af en medarbejder i en-til-en interaktion.</t>
+  </si>
+  <si>
+    <t>6b29554d-0261-4ec4-bb16-022d81c7dfb7</t>
+  </si>
+  <si>
+    <t>Type genoptræningsplan</t>
+  </si>
+  <si>
+    <t>0c8e2bfc-1350-45d1-90da-c07e2645d073</t>
+  </si>
+  <si>
+    <t>Specialiseret</t>
+  </si>
+  <si>
+    <t>Midlertidig kopi af MedComs kode for genoptræning på specialieret niveau, som specificeret af den gode genoptræningsplan, https://svn.medcom.dk/svn/releases/Standarder/National%20Sygehus-Kommunesamarbejde/GGOP/Dokumentation/GGOP.pdf</t>
+  </si>
+  <si>
+    <t>83c89857-8fb8-4163-97b1-eb1a56345c29</t>
+  </si>
+  <si>
+    <t>Rehabilitering</t>
+  </si>
+  <si>
+    <t>Midlertidig kopi af MedComs kode for rehabilitering på specialiseret niveau, som specificeret af den gode genoptræningsplan, https://svn.medcom.dk/svn/releases/Standarder/National%20Sygehus-Kommunesamarbejde/GGOP/Dokumentation/GGOP.pdf</t>
+  </si>
+  <si>
+    <t>8b962281-2ab6-4b10-9c91-4bac592d6d49</t>
+  </si>
+  <si>
+    <t>Basal</t>
+  </si>
+  <si>
+    <t>Almen genoptræning på basalt niveau</t>
+  </si>
+  <si>
+    <t>b679c454-2da2-46dd-9425-0e52d4aa2bf3</t>
+  </si>
+  <si>
+    <t>Avanceret</t>
+  </si>
+  <si>
+    <t>Almen genoptræning på avanceret niveau</t>
+  </si>
+  <si>
+    <t>ffd81f78-352e-4589-a195-5350dd1df2a4</t>
+  </si>
+  <si>
+    <t>Almen</t>
+  </si>
+  <si>
+    <t>Midlertidig kopi af MedComs kode for genoptræning på alment niveau, som specificeret af den gode genoptræningsplan, https://svn.medcom.dk/svn/releases/Standarder/National%20Sygehus-Kommunesamarbejde/GGOP/Dokumentation/GGOP.pdf</t>
+  </si>
+  <si>
+    <t>7b41185e-eeb4-437d-8120-5d51bbd27a79</t>
+  </si>
+  <si>
+    <t>Indsats/ydelses-anmodning</t>
+  </si>
+  <si>
+    <t>490ab7be-ddb1-4a54-baf1-009fe6e8a83b</t>
+  </si>
+  <si>
+    <t>Kommunal sygepleje</t>
+  </si>
+  <si>
+    <t>Der anmodes om kommunal sygepleje.</t>
+  </si>
+  <si>
+    <t>4a297733-4d66-4726-a933-590d55cf91e0</t>
+  </si>
+  <si>
+    <t>Der anmodes om en social indsats</t>
+  </si>
+  <si>
+    <t>7fc66c15-0cb3-4c89-9e18-f3a01e6a6592</t>
+  </si>
+  <si>
+    <t>Der anmodes om kommunal genoptræning efter sygehusophold efter SUL §140.</t>
+  </si>
+  <si>
+    <t>a71921ea-fe83-441d-933b-cc21d0b3c8c3</t>
+  </si>
+  <si>
+    <t>Der anmodes om kommunal sundhedsfremme og forebyggelse efter SUL §119.</t>
+  </si>
+  <si>
+    <t>ad865929-7363-4b2d-a271-01993181fbaf</t>
+  </si>
+  <si>
+    <t>Kommunal pleje og omsorg</t>
+  </si>
+  <si>
+    <t>Der anmodes om kommunal pleje og omsorg fx hjemmepleje til ældre borger.</t>
+  </si>
+  <si>
+    <t>d267ac44-8d7f-43e9-8535-ab3da350649f</t>
+  </si>
+  <si>
+    <t>Kommunalt hjælpemiddelområde</t>
+  </si>
+  <si>
+    <t>Der anmodes om hjælpemidler og lignende, der ligger indenfor det kommunale hjælpemiddelområde dvs § 112, § 113, § 114, § 116 i Serviceloven.</t>
+  </si>
+  <si>
+    <t>880028ec-5f16-4242-ba53-57a902094d5b</t>
+  </si>
+  <si>
+    <t>Deltagere i kontakt</t>
+  </si>
+  <si>
+    <t>ca228a58-bd0e-4b0e-81ce-3866adc26535</t>
+  </si>
+  <si>
+    <t>Barn/ung deltager</t>
+  </si>
+  <si>
+    <t>Behandler og barn/ung i målgruppen (5-17år) og evt. forældre, værger el.lign. er til stede. Barnet/den unge er genstand for journaloptagelsen.</t>
+  </si>
+  <si>
+    <t>d3578249-10df-4051-851d-3986b1570bee</t>
+  </si>
+  <si>
+    <t>Omsorgsperson uden barn/ung</t>
+  </si>
+  <si>
+    <t>Behandling hvor kun behandler og forældre, værger el.lign. til barn/ung er til stede. Barnet/den unge er genstand for journalen.</t>
+  </si>
+  <si>
+    <t>940f37e6-8a3d-483b-adac-be8af3268a5b</t>
+  </si>
+  <si>
+    <t>oplysningsaktivitet</t>
+  </si>
+  <si>
+    <t>0f0f223c-abe3-4720-aab8-c257679a0a4e</t>
+  </si>
+  <si>
+    <t>terapeutfaglig udredning, FSIII</t>
+  </si>
+  <si>
+    <t>udførelse af terapeutfaglig udredning jævnfør FSIII</t>
+  </si>
+  <si>
+    <t>47fd1468-89da-4803-9d7a-ecc039a30d92</t>
+  </si>
+  <si>
+    <t>sygeplejefaglig udredning, FSIII</t>
+  </si>
+  <si>
+    <t>udførelse af sygeplejefaglig udredning jævnfør FSIII</t>
+  </si>
+  <si>
+    <t>95e787e0-5490-437d-ae4c-f3736644242f</t>
+  </si>
+  <si>
+    <t>afklarende samtale §119, FSIII</t>
+  </si>
+  <si>
+    <t>udførelse af afklarende samtale vedr. sundhedsfremme og forebyggelse jævnfør FSIII</t>
+  </si>
+  <si>
+    <t>e5a73b0e-a5d2-430e-931f-6156306ab00f</t>
+  </si>
+  <si>
+    <t>funktionsevnevurdering hjemmepleje, FSIII</t>
+  </si>
+  <si>
+    <t>udførelse af funktionsevnevurdering i hjemmeplejen jævnfør FSIII</t>
+  </si>
+  <si>
+    <t>f8ebd11a-04f3-4aa0-9786-406e8896c84d</t>
+  </si>
+  <si>
+    <t>socialfaglig udredning, VUM/FFB</t>
+  </si>
+  <si>
+    <t>udførelse af socialfaglig udredning som specificeret af VUM og FFB</t>
+  </si>
+  <si>
+    <t>95ec4535-8fe8-4296-867c-35de421794cf</t>
+  </si>
+  <si>
+    <t>evaluering</t>
+  </si>
+  <si>
+    <t>053a301d-1bb8-4cc4-b781-87825ecf0ef8</t>
+  </si>
+  <si>
+    <t>FFB vurdering af borgers situation</t>
+  </si>
+  <si>
+    <t>Vurdering der sammenholder oplysninger fra udredning mhp en samlet faglig analyse og konklusion.</t>
+  </si>
+  <si>
+    <t>3f7a8ca0-afca-4b0d-8773-a99b5f2f8aaf</t>
+  </si>
+  <si>
+    <t>VUM Borgerens perspektiv på indsatsen</t>
+  </si>
+  <si>
+    <t>effe55c7-572c-4a99-8fb4-2a9dda2f6572</t>
+  </si>
+  <si>
+    <t>FFB støttebehovsvurdering</t>
+  </si>
+  <si>
+    <t>Angiver, hvor stort et behov borgeren har for hjælp og støtte.</t>
+  </si>
+  <si>
+    <t>f52887de-023f-4193-b6b0-4b0a37b1cffc</t>
+  </si>
+  <si>
+    <t>VUM Borgerens ressourcer i forhold til indsatsen</t>
+  </si>
+  <si>
+    <t>b5731132-f6b9-4a47-995d-681d2b755d4f</t>
+  </si>
+  <si>
+    <t>Kilde</t>
+  </si>
+  <si>
+    <t>Person der er kilde til oplysning eller vurdering</t>
+  </si>
+  <si>
+    <t>12428e48-7df8-441f-9a89-d92bb7874066</t>
+  </si>
+  <si>
+    <t>Borger støttet af medarbejder</t>
+  </si>
+  <si>
+    <t>Borger fik hjælp af en medarbejder til at komme med oplysninger eller vurderinger. Fx ældre borger der får hjælp til at udfylde WHO5 spørgeskema.</t>
+  </si>
+  <si>
+    <t>166d2437-4e47-4a52-bd94-cdbe91086ca6</t>
+  </si>
+  <si>
+    <t>Pårørende alene</t>
+  </si>
+  <si>
+    <t>Pårørende er alene, uden input fra borger, kilde til oplysninger eller vuderderinger. Fx WHO 5 spørgeskema for svækket ældre borger udfyldt af datter.</t>
+  </si>
+  <si>
+    <t>25b4e705-2e9a-47a2-b11a-c829316b9d3a</t>
+  </si>
+  <si>
+    <t>Borger</t>
+  </si>
+  <si>
+    <t>Borger er kilde til oplysning eller vurdering</t>
+  </si>
+  <si>
+    <t>329774f9-7700-47cf-9c00-63765d9e8078</t>
+  </si>
+  <si>
+    <t>Medarbejder og pårørende alene</t>
+  </si>
+  <si>
+    <t>En medarbejder og pårørende er sammen, men uden input fra borger, kilde til oplysning eller vurdering. Fx PUF spørgeskema i sundhedsplejen.</t>
+  </si>
+  <si>
+    <t>8fe80acb-2c2a-4f10-b2b8-ddb77d2f69dc</t>
+  </si>
+  <si>
+    <t>Medarbejder alene</t>
+  </si>
+  <si>
+    <t>Medarbejderen er alene kilde til oplysning eller vurdering. Fx AIMS skema i sundhedsplejen.</t>
+  </si>
+  <si>
+    <t>b66dc78a-a673-43fc-8ac0-1e859ba626e0</t>
+  </si>
+  <si>
+    <t>Borger støttet af pårørende</t>
+  </si>
+  <si>
+    <t>Borger fik hjælp af en pårørende til at komme med oplysninger eller vurderinger. Fx ældre borger der får hjælp til at udfylde WHO5 spørgeskema.</t>
+  </si>
+  <si>
+    <t>f6ea2920-7dde-491e-a489-6b99a3904069</t>
+  </si>
+  <si>
+    <t>Sagsbehandler</t>
+  </si>
+  <si>
+    <t>Sagsbehandler er kilde til oplysning eller vurdering</t>
+  </si>
+  <si>
+    <t>63338442-7b2e-405b-acc0-142361ef19f1</t>
+  </si>
+  <si>
+    <t>Andre</t>
+  </si>
+  <si>
+    <t>Andre end borger og sagsbehandler er kilde til oplysning eller vurdering. Fx læge, pårørende og udfører. Denne definition af andre, bruges kun på voksensocialområdet.</t>
+  </si>
+  <si>
+    <t>f00a6844-1005-401d-965d-1c5859df7beb</t>
+  </si>
+  <si>
+    <t>Udfører</t>
+  </si>
+  <si>
+    <t>Udfører er kilde til oplysning eller vurdering</t>
   </si>
   <si>
     <t>bb233864-6d4c-4ab4-a4a3-567e61b3dfb0</t>
@@ -757,6 +850,33 @@
     <t>Begrundelse for manglende aktivitet</t>
   </si>
   <si>
+    <t>3796fa11-305f-47d6-b164-45b05489afb2</t>
+  </si>
+  <si>
+    <t>Frit valg</t>
+  </si>
+  <si>
+    <t>Borger er overgået til frit valg af service. Fx frit valg af privat genoptræning som borger har ret til, hvis kommunen ikke kan levere inden 7 dage.</t>
+  </si>
+  <si>
+    <t>46a6bc1f-bfe8-4390-a71f-44ad4a384b9d</t>
+  </si>
+  <si>
+    <t>Frit valg afslået</t>
+  </si>
+  <si>
+    <t>Borgeren er tilbudt frit valg af leverandør af service, men vil hellere vente.</t>
+  </si>
+  <si>
+    <t>8ac7be88-5d16-4dbd-a61a-ab02673f4b34</t>
+  </si>
+  <si>
+    <t>Fejl</t>
+  </si>
+  <si>
+    <t>Fejlafsendt anmodning. Fx fejlafsendt genoptræningsplan.</t>
+  </si>
+  <si>
     <t>a8632e22-bf0c-4f5a-92a7-70977ba104d5</t>
   </si>
   <si>
@@ -775,142 +895,31 @@
     <t>Overgivet til anden kommune, på borgers anmodning</t>
   </si>
   <si>
-    <t>3796fa11-305f-47d6-b164-45b05489afb2</t>
-  </si>
-  <si>
-    <t>Frit valg</t>
-  </si>
-  <si>
-    <t>Borger er overgået til frit valg af service. Fx frit valg af privat genoptræning som borger har ret til, hvis kommunen ikke kan levere inden 7 dage.</t>
-  </si>
-  <si>
-    <t>8ac7be88-5d16-4dbd-a61a-ab02673f4b34</t>
-  </si>
-  <si>
-    <t>Fejl</t>
-  </si>
-  <si>
-    <t>Fejlafsendt anmodning. Fx fejlafsendt genoptræningsplan.</t>
-  </si>
-  <si>
-    <t>46a6bc1f-bfe8-4390-a71f-44ad4a384b9d</t>
-  </si>
-  <si>
-    <t>Frit valg afslået</t>
-  </si>
-  <si>
-    <t>Borgeren er tilbudt frit valg af leverandør af service, men vil hellere vente.</t>
-  </si>
-  <si>
-    <t>2c059407-fed5-4852-92d8-6bb5ad63d7bb</t>
-  </si>
-  <si>
-    <t>Begrundelse for indsatsophør</t>
-  </si>
-  <si>
-    <t>Begrundelse for, at kommunale indsatser ophører</t>
-  </si>
-  <si>
-    <t>82e99421-31da-4915-96ed-168ccfa1d20c</t>
-  </si>
-  <si>
-    <t>Hændelse medfører ophør</t>
-  </si>
-  <si>
-    <t>Hændelse, som ikke er et aktivt fravalg eller en behovsvurdering medfører ophør. Det kan fx være en længere hospitalsindlæggelse, eller at borger flytter.</t>
-  </si>
-  <si>
-    <t>4bbf6d6a-a1c6-41c2-b8c1-7352b7378adf</t>
-  </si>
-  <si>
-    <t>Ikke yderligere behov (borger-vurderet)</t>
-  </si>
-  <si>
-    <t>Borger vurderer, at han/hun ikke har yderligere behov og afslutter derfor før tid</t>
-  </si>
-  <si>
-    <t>a63b6aa6-7d56-4e67-a5b3-d73f6d262af5</t>
-  </si>
-  <si>
-    <t>Ikke yderligere behov (fagperson-vurderet)</t>
-  </si>
-  <si>
-    <t>Fagperson vurderer, at borger ikke har yderligere behov og afslutter derfor før tid</t>
-  </si>
-  <si>
-    <t>ef491570-7884-4acd-bcf7-43d6b2c64762</t>
-  </si>
-  <si>
-    <t>Borger har ikke henvendt sig eller er udeblevet</t>
-  </si>
-  <si>
-    <t>3a5a72b7-addf-4857-b80c-04e4246e3072</t>
-  </si>
-  <si>
-    <t>Aktivt fravalg</t>
-  </si>
-  <si>
-    <t>Borger har behov, men har foretaget et aktivt fravalg</t>
-  </si>
-  <si>
-    <t>8371b769-4bfb-4ac8-b130-d91c54784a56</t>
-  </si>
-  <si>
-    <t>Aktivt fravalg pga. logistik ifm. transport</t>
-  </si>
-  <si>
-    <t>Borger har behov, men har foretaget et aktivt fravalg pga. den logistiske udfordring det er mht. transport, at nå frem til det sted indsatsen tilbydes</t>
-  </si>
-  <si>
-    <t>a3f2bd01-078b-486e-81be-797d192ad7bd</t>
-  </si>
-  <si>
-    <t>Aktivt fravalg pga. anden træning</t>
-  </si>
-  <si>
-    <t>Borger har behov, men har foretaget et aktivt fravalg fordi han/hun er påbegyndt træning i andet regi fx fitnesscenter</t>
-  </si>
-  <si>
-    <t>0cd5734d-b663-47c6-a3da-6b14a937d144</t>
-  </si>
-  <si>
-    <t>Aktivt fravalg pga. anden sygdom</t>
-  </si>
-  <si>
-    <t>Borger har behov, men har foretaget et aktivt fravalg pga. anden sygdom</t>
-  </si>
-  <si>
-    <t>f8436c2e-af1c-44fe-939d-473b518dd01d</t>
-  </si>
-  <si>
-    <t>Aktivt fravalg pga. økonomi ifm. transport</t>
-  </si>
-  <si>
-    <t>Borger har behov, men har foretaget et aktivt fravalg pga. den omkostning der er forbundet med transport til det sted indsatsen tilbydes</t>
-  </si>
-  <si>
-    <t>880028ec-5f16-4242-ba53-57a902094d5b</t>
-  </si>
-  <si>
-    <t>Deltagere i kontakt</t>
-  </si>
-  <si>
-    <t>ca228a58-bd0e-4b0e-81ce-3866adc26535</t>
-  </si>
-  <si>
-    <t>Barn/ung deltager</t>
-  </si>
-  <si>
-    <t>Behandler og barn/ung i målgruppen (5-17år) og evt. forældre, værger el.lign. er til stede. Barnet/den unge er genstand for journaloptagelsen.</t>
-  </si>
-  <si>
-    <t>d3578249-10df-4051-851d-3986b1570bee</t>
-  </si>
-  <si>
-    <t>Omsorgsperson uden barn/ung</t>
-  </si>
-  <si>
-    <t>Behandling hvor kun behandler og forældre, værger el.lign. til barn/ung er til stede. Barnet/den unge er genstand for journalen.</t>
+    <t>bf469e95-f9e3-45c7-bf15-ab7e8a85236f</t>
+  </si>
+  <si>
+    <t>Kontaktklasse</t>
+  </si>
+  <si>
+    <t>Type af kontakt. Beskriver leveringsmetode.</t>
+  </si>
+  <si>
+    <t>124be95d-6924-4609-9d2a-e7c73ae3ab3d</t>
+  </si>
+  <si>
+    <t>Skærmbesøg</t>
+  </si>
+  <si>
+    <t>Kontakten er foregået via skærm med mulighed for tændt kamera, så parterne har haft mulighed for at interagere ansigt til ansigt, og fremvise ting.</t>
+  </si>
+  <si>
+    <t>1b55a4b0-1156-4f58-b2df-b5c6014d9048</t>
+  </si>
+  <si>
+    <t>Telefonisk</t>
+  </si>
+  <si>
+    <t>Kontakten er foregået per telefon.</t>
   </si>
 </sst>
 </file>
@@ -1220,7 +1229,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D92"/>
+  <dimension ref="A1:D93"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1290,35 +1299,35 @@
         <v>51</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8">
@@ -1326,55 +1335,55 @@
         <v>43</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12">
@@ -1382,13 +1391,13 @@
         <v>43</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13">
@@ -1396,13 +1405,13 @@
         <v>43</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14">
@@ -1410,13 +1419,13 @@
         <v>40</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15">
@@ -1424,13 +1433,13 @@
         <v>43</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1438,13 +1447,13 @@
         <v>43</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17">
@@ -1452,13 +1461,13 @@
         <v>43</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18">
@@ -1466,13 +1475,13 @@
         <v>43</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19">
@@ -1480,83 +1489,83 @@
         <v>43</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D22" t="s" s="2">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>101</v>
+        <v>40</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D23" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D24" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="25">
@@ -1564,13 +1573,13 @@
         <v>43</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="26">
@@ -1578,13 +1587,13 @@
         <v>43</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D26" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="27">
@@ -1592,13 +1601,13 @@
         <v>43</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D27" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="28">
@@ -1606,13 +1615,13 @@
         <v>43</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D28" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="29">
@@ -1620,10 +1629,10 @@
         <v>43</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D29" t="s" s="2">
         <v>122</v>
@@ -1631,7 +1640,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>123</v>
@@ -1659,7 +1668,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>129</v>
@@ -1668,7 +1677,7 @@
         <v>130</v>
       </c>
       <c r="D32" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="33">
@@ -1676,13 +1685,13 @@
         <v>43</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D33" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="34">
@@ -1690,10 +1699,10 @@
         <v>43</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>136</v>
@@ -1701,7 +1710,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>137</v>
@@ -1710,74 +1719,74 @@
         <v>138</v>
       </c>
       <c r="D35" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D36" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D37" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D38" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D39" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D40" t="s" s="2">
         <v>153</v>
@@ -1794,35 +1803,35 @@
         <v>155</v>
       </c>
       <c r="D41" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D42" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D43" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="44">
@@ -1830,13 +1839,13 @@
         <v>43</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D44" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="45">
@@ -1844,13 +1853,13 @@
         <v>43</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D45" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="46">
@@ -1858,13 +1867,13 @@
         <v>43</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D46" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="47">
@@ -1872,13 +1881,13 @@
         <v>43</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D47" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="48">
@@ -1886,13 +1895,13 @@
         <v>40</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D48" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="49">
@@ -1900,13 +1909,13 @@
         <v>43</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>57</v>
+        <v>178</v>
       </c>
       <c r="D49" t="s" s="2">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="50">
@@ -1914,13 +1923,13 @@
         <v>43</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D50" t="s" s="2">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="51">
@@ -1928,97 +1937,97 @@
         <v>43</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>66</v>
+        <v>184</v>
       </c>
       <c r="D51" t="s" s="2">
-        <v>181</v>
+        <v>185</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>101</v>
+        <v>43</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="D52" t="s" s="2">
-        <v>184</v>
+        <v>188</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>101</v>
+        <v>43</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="D53" t="s" s="2">
-        <v>187</v>
+        <v>191</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>69</v>
+        <v>193</v>
       </c>
       <c r="D54" t="s" s="2">
-        <v>189</v>
+        <v>193</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>101</v>
+        <v>43</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="D55" t="s" s="2">
-        <v>192</v>
+        <v>196</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>101</v>
+        <v>43</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>194</v>
+        <v>48</v>
       </c>
       <c r="D56" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>197</v>
+        <v>61</v>
       </c>
       <c r="D57" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="58">
@@ -2026,13 +2035,13 @@
         <v>43</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>200</v>
+        <v>51</v>
       </c>
       <c r="D58" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="59">
@@ -2040,41 +2049,41 @@
         <v>43</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D59" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D60" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D61" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="62">
@@ -2082,41 +2091,41 @@
         <v>43</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D62" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D63" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D64" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="65">
@@ -2124,13 +2133,13 @@
         <v>43</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D65" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="66">
@@ -2138,13 +2147,13 @@
         <v>43</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D66" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="67">
@@ -2152,13 +2161,13 @@
         <v>43</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D67" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="68">
@@ -2166,38 +2175,38 @@
         <v>43</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D68" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D69" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D70" t="s" s="2">
         <v>235</v>
@@ -2228,7 +2237,7 @@
         <v>240</v>
       </c>
       <c r="D72" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="73">
@@ -2236,41 +2245,41 @@
         <v>43</v>
       </c>
       <c r="B73" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="C73" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="C73" t="s" s="2">
+      <c r="D73" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="D73" t="s" s="2">
-        <v>244</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B74" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="C74" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="C74" t="s" s="2">
-        <v>246</v>
-      </c>
       <c r="D74" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B75" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="C75" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="C75" t="s" s="2">
+      <c r="D75" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="D75" t="s" s="2">
-        <v>249</v>
       </c>
     </row>
     <row r="76">
@@ -2278,13 +2287,13 @@
         <v>43</v>
       </c>
       <c r="B76" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="C76" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="C76" t="s" s="2">
+      <c r="D76" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="D76" t="s" s="2">
-        <v>252</v>
       </c>
     </row>
     <row r="77">
@@ -2292,13 +2301,13 @@
         <v>43</v>
       </c>
       <c r="B77" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="C77" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="C77" t="s" s="2">
+      <c r="D77" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="D77" t="s" s="2">
-        <v>255</v>
       </c>
     </row>
     <row r="78">
@@ -2306,13 +2315,13 @@
         <v>43</v>
       </c>
       <c r="B78" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="C78" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="C78" t="s" s="2">
+      <c r="D78" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="D78" t="s" s="2">
-        <v>258</v>
       </c>
     </row>
     <row r="79">
@@ -2320,27 +2329,27 @@
         <v>43</v>
       </c>
       <c r="B79" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="C79" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="C79" t="s" s="2">
+      <c r="D79" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="D79" t="s" s="2">
-        <v>261</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B80" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="C80" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="C80" t="s" s="2">
+      <c r="D80" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="D80" t="s" s="2">
-        <v>264</v>
       </c>
     </row>
     <row r="81">
@@ -2348,13 +2357,13 @@
         <v>43</v>
       </c>
       <c r="B81" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="C81" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="C81" t="s" s="2">
+      <c r="D81" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="D81" t="s" s="2">
-        <v>267</v>
       </c>
     </row>
     <row r="82">
@@ -2362,13 +2371,13 @@
         <v>43</v>
       </c>
       <c r="B82" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="C82" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="C82" t="s" s="2">
+      <c r="D82" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="D82" t="s" s="2">
-        <v>270</v>
       </c>
     </row>
     <row r="83">
@@ -2376,24 +2385,24 @@
         <v>43</v>
       </c>
       <c r="B83" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="C83" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="C83" t="s" s="2">
+      <c r="D83" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="D83" t="s" s="2">
-        <v>273</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="B84" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="C84" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="C84" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="D84" t="s" s="2">
         <v>275</v>
@@ -2401,7 +2410,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B85" t="s" s="2">
         <v>276</v>
@@ -2410,74 +2419,74 @@
         <v>277</v>
       </c>
       <c r="D85" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>101</v>
+        <v>43</v>
       </c>
       <c r="B86" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="C86" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="C86" t="s" s="2">
+      <c r="D86" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="D86" t="s" s="2">
-        <v>281</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>101</v>
+        <v>43</v>
       </c>
       <c r="B87" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="C87" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="C87" t="s" s="2">
+      <c r="D87" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="D87" t="s" s="2">
-        <v>284</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>101</v>
+        <v>43</v>
       </c>
       <c r="B88" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="C88" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="C88" t="s" s="2">
+      <c r="D88" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="D88" t="s" s="2">
-        <v>287</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>101</v>
+        <v>43</v>
       </c>
       <c r="B89" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="C89" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="C89" t="s" s="2">
+      <c r="D89" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="D89" t="s" s="2">
-        <v>290</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B90" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="C90" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="C90" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="D90" t="s" s="2">
         <v>292</v>
@@ -2485,7 +2494,7 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B91" t="s" s="2">
         <v>293</v>
@@ -2509,6 +2518,20 @@
       </c>
       <c r="D92" t="s" s="2">
         <v>298</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="C93" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="D93" t="s" s="2">
+        <v>301</v>
       </c>
     </row>
   </sheetData>
